--- a/artfynd/A 7495-2026 artfynd.xlsx
+++ b/artfynd/A 7495-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111943234</v>
+        <v>111943322</v>
       </c>
       <c r="B2" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>833168</v>
+        <v>833195</v>
       </c>
       <c r="R2" t="n">
-        <v>7393327</v>
+        <v>7393378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,33 +757,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111943163</v>
+        <v>111943460</v>
       </c>
       <c r="B3" t="n">
-        <v>88180</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,35 +791,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kentholmen (Kentholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>833078</v>
+        <v>833357</v>
       </c>
       <c r="R3" t="n">
-        <v>7393403</v>
+        <v>7393365</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,69 +862,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111943428</v>
+        <v>111943641</v>
       </c>
       <c r="B4" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>833305</v>
+        <v>833294</v>
       </c>
       <c r="R4" t="n">
-        <v>7393357</v>
+        <v>7393486</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,33 +967,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111944303</v>
+        <v>111943878</v>
       </c>
       <c r="B5" t="n">
-        <v>90802</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,17 +1019,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>833228</v>
+        <v>833219</v>
       </c>
       <c r="R5" t="n">
-        <v>7393397</v>
+        <v>7393419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,33 +1072,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111943722</v>
+        <v>111944303</v>
       </c>
       <c r="B6" t="n">
-        <v>89036</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,37 +1106,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>245044</v>
+        <v>149</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>833228</v>
       </c>
       <c r="R6" t="n">
-        <v>7393401</v>
+        <v>7393397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,74 +1175,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111943441</v>
+        <v>111943420</v>
       </c>
       <c r="B7" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>1593</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>833340</v>
+        <v>833275</v>
       </c>
       <c r="R7" t="n">
-        <v>7393352</v>
+        <v>7393342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,71 +1275,69 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111943635</v>
+        <v>111943253</v>
       </c>
       <c r="B8" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>833333</v>
+        <v>833146</v>
       </c>
       <c r="R8" t="n">
-        <v>7393500</v>
+        <v>7393366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,38 +1378,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111943614</v>
+        <v>111943212</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1426,37 +1407,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>833333</v>
+        <v>833120</v>
       </c>
       <c r="R9" t="n">
-        <v>7393500</v>
+        <v>7393354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,76 +1476,64 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111943656</v>
+        <v>111943428</v>
       </c>
       <c r="B10" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>833289</v>
+        <v>833305</v>
       </c>
       <c r="R10" t="n">
-        <v>7393475</v>
+        <v>7393357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,38 +1574,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111943668</v>
+        <v>111944274</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,14 +1626,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>833267</v>
+        <v>833096</v>
       </c>
       <c r="R11" t="n">
-        <v>7393401</v>
+        <v>7393463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,21 +1691,16 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111943166</v>
+        <v>111943307</v>
       </c>
       <c r="B12" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,35 +1708,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kentholmen (Kentholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>833041</v>
+        <v>833184</v>
       </c>
       <c r="R12" t="n">
-        <v>7393426</v>
+        <v>7393362</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,33 +1779,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111943427</v>
+        <v>111943579</v>
       </c>
       <c r="B13" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,14 +1836,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>833316</v>
+        <v>833442</v>
       </c>
       <c r="R13" t="n">
-        <v>7393384</v>
+        <v>7393431</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,21 +1901,16 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111943254</v>
+        <v>111943582</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,37 +1918,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>833174</v>
+        <v>833363</v>
       </c>
       <c r="R14" t="n">
-        <v>7393370</v>
+        <v>7393372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,38 +1987,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111943639</v>
+        <v>111943669</v>
       </c>
       <c r="B15" t="n">
-        <v>91232</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,37 +2016,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>833333</v>
+        <v>833248</v>
       </c>
       <c r="R15" t="n">
-        <v>7393500</v>
+        <v>7393392</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,38 +2085,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111943212</v>
+        <v>111943166</v>
       </c>
       <c r="B16" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,35 +2114,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Kentholmen, Kentholmen, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>833120</v>
+        <v>833042</v>
       </c>
       <c r="R16" t="n">
-        <v>7393354</v>
+        <v>7393426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2276,15 +2201,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111943242</v>
+        <v>111943254</v>
       </c>
       <c r="B17" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,21 +2212,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,14 +2235,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>833156</v>
+        <v>833174</v>
       </c>
       <c r="R17" t="n">
-        <v>7393339</v>
+        <v>7393370</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,59 +2300,52 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111943420</v>
+        <v>111943426</v>
       </c>
       <c r="B18" t="n">
-        <v>88985</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1593</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>833275</v>
+        <v>833304</v>
       </c>
       <c r="R18" t="n">
-        <v>7393342</v>
+        <v>7393352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,60 +2386,50 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111943641</v>
+        <v>111943427</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2535,14 +2438,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>833294</v>
+        <v>833316</v>
       </c>
       <c r="R19" t="n">
-        <v>7393486</v>
+        <v>7393384</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,21 +2503,16 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111943582</v>
+        <v>111943441</v>
       </c>
       <c r="B20" t="n">
-        <v>85403</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,35 +2520,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3690</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>833363</v>
+        <v>833340</v>
       </c>
       <c r="R20" t="n">
-        <v>7393372</v>
+        <v>7393351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2709,15 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111943511</v>
+        <v>111943607</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,14 +2641,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>833451</v>
+        <v>833353</v>
       </c>
       <c r="R21" t="n">
-        <v>7393385</v>
+        <v>7393482</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2813,21 +2706,16 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111943426</v>
+        <v>111943668</v>
       </c>
       <c r="B22" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2853,17 +2741,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>833303</v>
+        <v>833267</v>
       </c>
       <c r="R22" t="n">
-        <v>7393352</v>
+        <v>7393401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,55 +2794,55 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111943492</v>
+        <v>111943511</v>
       </c>
       <c r="B23" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,14 +2851,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>833369</v>
+        <v>833451</v>
       </c>
       <c r="R23" t="n">
-        <v>7393392</v>
+        <v>7393385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,21 +2916,16 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111943669</v>
+        <v>111943614</v>
       </c>
       <c r="B24" t="n">
-        <v>85403</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3048,35 +2933,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>833249</v>
+        <v>833333</v>
       </c>
       <c r="R24" t="n">
-        <v>7393392</v>
+        <v>7393500</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3117,33 +3004,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111943253</v>
+        <v>111944106</v>
       </c>
       <c r="B25" t="n">
-        <v>90830</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,35 +3038,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>833146</v>
+        <v>833219</v>
       </c>
       <c r="R25" t="n">
-        <v>7393366</v>
+        <v>7393413</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,69 +3109,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111943458</v>
+        <v>111943251</v>
       </c>
       <c r="B26" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>833349</v>
+        <v>833166</v>
       </c>
       <c r="R26" t="n">
-        <v>7393362</v>
+        <v>7393365</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,55 +3214,55 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111943179</v>
+        <v>111943635</v>
       </c>
       <c r="B27" t="n">
-        <v>88203</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6286</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3380,14 +3271,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kentholmen (Kentholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>833066</v>
+        <v>833333</v>
       </c>
       <c r="R27" t="n">
-        <v>7393396</v>
+        <v>7393500</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,27 +3326,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111943501</v>
+        <v>111943656</v>
       </c>
       <c r="B28" t="n">
-        <v>90858</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,35 +3353,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>833338</v>
+        <v>833289</v>
       </c>
       <c r="R28" t="n">
-        <v>7393366</v>
+        <v>7393475</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,69 +3424,71 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111943642</v>
+        <v>111943095</v>
       </c>
       <c r="B29" t="n">
-        <v>88203</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Kentholmen, Kentholmen, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>833307</v>
+        <v>833000</v>
       </c>
       <c r="R29" t="n">
-        <v>7393495</v>
+        <v>7393456</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,6 +3529,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3653,15 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111943307</v>
+        <v>111943234</v>
       </c>
       <c r="B30" t="n">
-        <v>86195</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,37 +3559,35 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>833184</v>
+        <v>833168</v>
       </c>
       <c r="R30" t="n">
-        <v>7393362</v>
+        <v>7393327</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,38 +3628,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111943600</v>
+        <v>111943432</v>
       </c>
       <c r="B31" t="n">
-        <v>91232</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3802,14 +3680,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>833377</v>
+        <v>833358</v>
       </c>
       <c r="R31" t="n">
-        <v>7393501</v>
+        <v>7393336</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,21 +3745,16 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111943432</v>
+        <v>111943458</v>
       </c>
       <c r="B32" t="n">
-        <v>91232</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,19 +3780,17 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>833358</v>
+        <v>833350</v>
       </c>
       <c r="R32" t="n">
-        <v>7393336</v>
+        <v>7393362</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,38 +3831,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111943607</v>
+        <v>111943600</v>
       </c>
       <c r="B33" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3999,21 +3860,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,14 +3883,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>833353</v>
+        <v>833377</v>
       </c>
       <c r="R33" t="n">
-        <v>7393482</v>
+        <v>7393501</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4087,43 +3948,38 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111943251</v>
+        <v>111943639</v>
       </c>
       <c r="B34" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4132,14 +3988,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Furuholmen, Furuholmen, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>833166</v>
+        <v>833333</v>
       </c>
       <c r="R34" t="n">
-        <v>7393365</v>
+        <v>7393500</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4197,21 +4053,16 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111943460</v>
+        <v>111943090</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4219,37 +4070,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Kentholmen, Kentholmen, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>833357</v>
+        <v>833002</v>
       </c>
       <c r="R35" t="n">
-        <v>7393365</v>
+        <v>7393458</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,38 +4139,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Sandtallskogsprojektet 2023-2024, Norrbottens län</t>
-        </is>
-      </c>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111943224</v>
+        <v>111943163</v>
       </c>
       <c r="B36" t="n">
-        <v>88203</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,37 +4168,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Furuholmen (Furuholmen), Nb</t>
+          <t>Kentholmen, Kentholmen, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>833151</v>
+        <v>833078</v>
       </c>
       <c r="R36" t="n">
-        <v>7393350</v>
+        <v>7393404</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4237,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4416,6 +4252,837 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>111943492</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Furuholmen, Furuholmen, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>833369</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7393392</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111943179</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kentholmen, Kentholmen, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>833066</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7393396</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111943224</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Furuholmen, Furuholmen, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>833150</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7393351</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111943575</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Furuholmen, Furuholmen, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>833435</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7393445</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>111943642</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Furuholmen, Furuholmen, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>833307</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7393495</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>111944227</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Furuholmen, Furuholmen, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>833214</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7393402</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>62390039</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90699</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>245044</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tallmusseron</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tricholoma roseoacerbum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>A.Riva</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lansåheden, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>833133</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7393444</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2016-09-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2016-09-16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sture Westerberg, Hanna Engström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>111943722</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90699</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>245044</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tallmusseron</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tricholoma roseoacerbum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>A.Riva</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Furuholmen, Furuholmen, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>833228</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7393401</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
